--- a/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
@@ -5794,7 +5794,9 @@
         <v>3.0</v>
       </c>
       <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
+      <c r="Q17" s="13">
+        <v>4.0</v>
+      </c>
       <c r="R17" s="11"/>
       <c r="S17" s="23"/>
     </row>

--- a/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
@@ -735,7 +735,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -748,6 +748,9 @@
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -770,9 +773,6 @@
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -792,7 +792,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2053,7 +2053,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="45.43"/>
+    <col customWidth="1" min="8" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="28.71"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -2168,7 +2172,9 @@
         <v>5.0</v>
       </c>
       <c r="P2" s="6"/>
-      <c r="Q2" s="9"/>
+      <c r="Q2" s="9">
+        <v>4.0</v>
+      </c>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="10"/>
@@ -2225,7 +2231,7 @@
         <v>5.0</v>
       </c>
       <c r="P3" s="11"/>
-      <c r="Q3" s="9"/>
+      <c r="Q3" s="14"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10"/>
@@ -2266,19 +2272,23 @@
       <c r="H4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="15">
         <v>1.2822E11</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="16"/>
       <c r="K4" s="13">
         <v>3.0</v>
       </c>
       <c r="L4" s="11"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="9">
+        <v>4.0</v>
+      </c>
       <c r="N4" s="11"/>
-      <c r="O4" s="9"/>
+      <c r="O4" s="9">
+        <v>3.0</v>
+      </c>
       <c r="P4" s="11"/>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="14"/>
       <c r="R4" s="11"/>
       <c r="S4" s="13">
         <v>5.0</v>
@@ -2321,10 +2331,10 @@
       <c r="H5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="15">
         <v>1.28982E11</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="16">
         <f>I5/I4-1</f>
         <v>0.005942910622</v>
       </c>
@@ -2332,11 +2342,15 @@
         <v>3.0</v>
       </c>
       <c r="L5" s="11"/>
-      <c r="M5" s="9"/>
+      <c r="M5" s="9">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="11"/>
-      <c r="O5" s="9"/>
+      <c r="O5" s="9">
+        <v>3.0</v>
+      </c>
       <c r="P5" s="11"/>
-      <c r="Q5" s="9"/>
+      <c r="Q5" s="14"/>
       <c r="R5" s="11"/>
       <c r="S5" s="13">
         <v>5.0</v>
@@ -2375,7 +2389,7 @@
       <c r="H6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="11"/>
@@ -2383,11 +2397,15 @@
         <v>3.0</v>
       </c>
       <c r="L6" s="11"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="9">
+        <v>3.0</v>
+      </c>
       <c r="N6" s="11"/>
-      <c r="O6" s="9"/>
+      <c r="O6" s="9">
+        <v>4.0</v>
+      </c>
       <c r="P6" s="11"/>
-      <c r="Q6" s="9"/>
+      <c r="Q6" s="14"/>
       <c r="R6" s="11"/>
       <c r="S6" s="13">
         <v>5.0</v>
@@ -2668,7 +2686,7 @@
       <c r="H11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="17" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="11"/>
@@ -2732,7 +2750,7 @@
       <c r="I12" s="11">
         <v>8.2717481311E10</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="16"/>
       <c r="K12" s="13">
         <v>4.0</v>
       </c>
@@ -2837,7 +2855,7 @@
       <c r="H14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="17" t="s">
         <v>51</v>
       </c>
       <c r="J14" s="11"/>
@@ -2894,10 +2912,10 @@
       <c r="H15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="18">
         <v>3.8722294E9</v>
       </c>
-      <c r="J15" s="18"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="8">
         <v>5.0</v>
       </c>
@@ -3077,7 +3095,7 @@
       <c r="H18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <v>7.310367892E9</v>
       </c>
       <c r="J18" s="11"/>
@@ -3132,7 +3150,7 @@
       <c r="H19" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="21" t="s">
         <v>57</v>
       </c>
       <c r="J19" s="6"/>
@@ -3901,13 +3919,21 @@
         <v>5.0</v>
       </c>
       <c r="L32" s="11"/>
-      <c r="M32" s="21"/>
+      <c r="M32" s="9">
+        <v>4.0</v>
+      </c>
       <c r="N32" s="11"/>
-      <c r="O32" s="21"/>
+      <c r="O32" s="9">
+        <v>2.0</v>
+      </c>
       <c r="P32" s="11"/>
-      <c r="Q32" s="9"/>
+      <c r="Q32" s="9">
+        <v>2.0</v>
+      </c>
       <c r="R32" s="11"/>
-      <c r="S32" s="9"/>
+      <c r="S32" s="9">
+        <v>3.0</v>
+      </c>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
@@ -3952,13 +3978,21 @@
         <v>5.0</v>
       </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="21"/>
+      <c r="M33" s="9">
+        <v>4.0</v>
+      </c>
       <c r="N33" s="6"/>
-      <c r="O33" s="21"/>
+      <c r="O33" s="9">
+        <v>2.0</v>
+      </c>
       <c r="P33" s="6"/>
-      <c r="Q33" s="9"/>
+      <c r="Q33" s="9">
+        <v>2.0</v>
+      </c>
       <c r="R33" s="6"/>
-      <c r="S33" s="9"/>
+      <c r="S33" s="9">
+        <v>3.0</v>
+      </c>
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
@@ -4960,7 +4994,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="30.14"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -5600,13 +5636,21 @@
         <v>5.0</v>
       </c>
       <c r="L13" s="22"/>
-      <c r="M13" s="9"/>
+      <c r="M13" s="9">
+        <v>4.0</v>
+      </c>
       <c r="N13" s="11"/>
-      <c r="O13" s="9"/>
+      <c r="O13" s="9">
+        <v>3.0</v>
+      </c>
       <c r="P13" s="11"/>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="9">
+        <v>2.0</v>
+      </c>
       <c r="R13" s="11"/>
-      <c r="S13" s="28"/>
+      <c r="S13" s="28">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="11" t="s">
@@ -7115,7 +7159,7 @@
       <c r="H4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="21" t="s">
         <v>149</v>
       </c>
       <c r="J4" s="25"/>

--- a/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Secretaría General De La Alcaldía Mayor De Bogotá.xlsx
@@ -441,7 +441,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -450,7 +450,7 @@
     <t>Programas de sensibilización sobre innovación pública., Espacios de ideación y cocreación con los equipos internos., Incentivos o reconocimientos a iniciativas innovadoras de los funcionarios., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -5852,7 +5852,7 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>131</v>
       </c>
       <c r="E18" s="6"/>
@@ -5895,7 +5895,7 @@
       <c r="C19" s="12">
         <v>18.0</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="13" t="s">
         <v>134</v>
       </c>
       <c r="E19" s="11"/>
@@ -5940,7 +5940,7 @@
       <c r="C20" s="12">
         <v>19.0</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="13" t="s">
         <v>137</v>
       </c>
       <c r="E20" s="11" t="s">
